--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92759</v>
+        <v>92764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128634529</v>
+        <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>479224</v>
       </c>
       <c r="R7" t="n">
-        <v>6865357</v>
+        <v>6865355</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128634598</v>
+        <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>479224</v>
       </c>
       <c r="R8" t="n">
-        <v>6865355</v>
+        <v>6865357</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,48 +1562,62 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128634881</v>
+        <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>78749</v>
+        <v>92748</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stentjärnarna, Stentjärnarna, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479172</v>
+        <v>479137</v>
       </c>
       <c r="R11" t="n">
-        <v>6865294</v>
+        <v>6865035</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1659,62 +1673,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128635753</v>
+        <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>92743</v>
+        <v>78753</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stentjärnarna, Stentjärnarna, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479137</v>
+        <v>479172</v>
       </c>
       <c r="R12" t="n">
-        <v>6865035</v>
+        <v>6865294</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92737</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92764</v>
+        <v>92770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
+        <v>78432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78695</v>
+        <v>78700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92822</v>
+        <v>92827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78432</v>
+        <v>78437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78695</v>
+        <v>78700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78695</v>
+        <v>78700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2025 artfynd.xlsx
+++ b/artfynd/A 42157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635433</v>
       </c>
       <c r="B2" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128636156</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128636045</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128635821</v>
       </c>
       <c r="B5" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128635323</v>
       </c>
       <c r="B6" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128634598</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128634529</v>
       </c>
       <c r="B8" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128635626</v>
       </c>
       <c r="B9" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128635146</v>
       </c>
       <c r="B10" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128635753</v>
       </c>
       <c r="B11" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128634881</v>
       </c>
       <c r="B12" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128635259</v>
       </c>
       <c r="B13" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128634861</v>
       </c>
       <c r="B14" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128635067</v>
       </c>
       <c r="B15" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128635956</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128635553</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
